--- a/data/trans_camb/P12_2_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 0,83</t>
+          <t>-7,31; 0,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 2,26</t>
+          <t>-6,33; 2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,95</t>
+          <t>-6,68; 2,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -2,15</t>
+          <t>-9,92; -2,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 1,15</t>
+          <t>-7,23; 0,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,63; -1,96</t>
+          <t>-9,67; -1,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -1,87</t>
+          <t>-7,37; -1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,47</t>
+          <t>-5,78; 0,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -0,89</t>
+          <t>-6,93; -1,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 2,78</t>
+          <t>-22,26; 1,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 7,57</t>
+          <t>-19,39; 8,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 10,28</t>
+          <t>-20,48; 7,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -5,49</t>
+          <t>-22,84; -5,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 2,76</t>
+          <t>-16,98; 2,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -5,11</t>
+          <t>-22,47; -4,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -5,19</t>
+          <t>-19,02; -4,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 1,26</t>
+          <t>-15,18; 1,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -2,4</t>
+          <t>-18,21; -2,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,37</t>
+          <t>-3,13; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,21</t>
+          <t>-4,43; 0,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 1,42</t>
+          <t>-5,3; 1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,49</t>
+          <t>-4,13; 1,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -2,21</t>
+          <t>-7,58; -1,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -0,33</t>
+          <t>-8,36; -0,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,66</t>
+          <t>-3,01; 0,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; -1,75</t>
+          <t>-5,1; -1,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,1</t>
+          <t>-5,42; 0,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 10,89</t>
+          <t>-20,44; 11,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 1,68</t>
+          <t>-28,99; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 10,08</t>
+          <t>-36,59; 10,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 7,26</t>
+          <t>-18,14; 8,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,31; -10,95</t>
+          <t>-33,28; -9,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,78; -1,67</t>
+          <t>-37,18; -1,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 4,08</t>
+          <t>-16,46; 3,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,83; -10,38</t>
+          <t>-27,84; -10,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,27; -0,85</t>
+          <t>-29,3; -0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 2,53</t>
+          <t>-6,09; 3,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 0,4</t>
+          <t>-7,7; 0,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,77</t>
+          <t>-3,64; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -2,45</t>
+          <t>-12,57; -2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -5,09</t>
+          <t>-15,26; -5,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -1,22</t>
+          <t>-11,09; -1,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,74</t>
+          <t>-8,15; -0,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -3,46</t>
+          <t>-9,98; -3,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,87</t>
+          <t>-5,43; 0,99</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 18,82</t>
+          <t>-35,45; 23,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 3,42</t>
+          <t>-45,22; 4,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 36,23</t>
+          <t>-20,74; 38,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,36; -10,84</t>
+          <t>-46,87; -8,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,75; -23,2</t>
+          <t>-55,54; -22,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,2; -4,78</t>
+          <t>-40,02; -4,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,25; -4,24</t>
+          <t>-38,18; -5,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,38; -18,64</t>
+          <t>-46,71; -19,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 4,88</t>
+          <t>-25,2; 5,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,2</t>
+          <t>-4,23; -0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -2,05</t>
+          <t>-5,78; -2,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,48</t>
+          <t>-7,12; -1,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -2,1</t>
+          <t>-6,5; -2,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -5,32</t>
+          <t>-9,37; -5,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -5,74</t>
+          <t>-11,99; -5,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,63</t>
+          <t>-4,71; -1,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -4,05</t>
+          <t>-7,05; -4,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -4,18</t>
+          <t>-8,46; -4,07</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -1,01</t>
+          <t>-20,9; -2,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,69; -10,55</t>
+          <t>-27,76; -12,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,25; -7,87</t>
+          <t>-36,38; -8,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,46; -7,26</t>
+          <t>-20,79; -6,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,9; -18,72</t>
+          <t>-30,74; -17,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,62; -19,88</t>
+          <t>-40,35; -19,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,19; -6,8</t>
+          <t>-18,53; -6,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,69; -17,24</t>
+          <t>-27,78; -17,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -17,43</t>
+          <t>-34,38; -17,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_2_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,0</t>
+          <t>-6,65</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,06</t>
+          <t>-4,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 0,48</t>
+          <t>-7,22; 0,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,52</t>
+          <t>-6,42; 2,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,27</t>
+          <t>-7,54; 1,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; -2,02</t>
+          <t>-9,85; -1,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,92</t>
+          <t>-7,51; 0,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -1,85</t>
+          <t>-10,48; -3,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -1,61</t>
+          <t>-7,68; -1,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,38</t>
+          <t>-5,68; 0,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,0</t>
+          <t>-7,89; -1,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,84%</t>
+          <t>-10,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-14,46%</t>
+          <t>-16,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-11,02%</t>
+          <t>-13,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 1,78</t>
+          <t>-22,12; 3,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 8,96</t>
+          <t>-19,55; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 7,92</t>
+          <t>-23,38; 3,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -5,09</t>
+          <t>-22,88; -4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 2,27</t>
+          <t>-17,51; 2,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,47; -4,84</t>
+          <t>-24,0; -7,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -4,58</t>
+          <t>-19,95; -5,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 1,05</t>
+          <t>-15,03; 0,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,21; -2,84</t>
+          <t>-20,89; -5,09</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,76</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-0,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,51</t>
+          <t>-3,05; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,13</t>
+          <t>-4,31; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 1,4</t>
+          <t>-1,96; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,64</t>
+          <t>-4,13; 1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -1,93</t>
+          <t>-7,63; -2,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -0,38</t>
+          <t>-3,48; 1,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,59</t>
+          <t>-2,85; 0,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,62</t>
+          <t>-5,17; -1,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,0</t>
+          <t>-1,99; 1,57</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,61%</t>
+          <t>-4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,82%</t>
+          <t>-1,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 11,76</t>
+          <t>-19,86; 12,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 1,46</t>
+          <t>-28,27; 1,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 10,09</t>
+          <t>-12,82; 19,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 8,45</t>
+          <t>-18,65; 8,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,28; -9,75</t>
+          <t>-33,2; -10,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,18; -1,9</t>
+          <t>-15,36; 7,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 3,13</t>
+          <t>-15,53; 4,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -10,04</t>
+          <t>-27,93; -10,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -0,08</t>
+          <t>-10,85; 9,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,8</t>
+          <t>-4,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-1,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,1</t>
+          <t>-6,7; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 0,72</t>
+          <t>-7,99; 0,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,98</t>
+          <t>-3,35; 5,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -2,11</t>
+          <t>-12,86; -1,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -5,15</t>
+          <t>-15,49; -4,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,09; -1,04</t>
+          <t>-9,59; 0,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -0,88</t>
+          <t>-7,9; -0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -3,47</t>
+          <t>-10,12; -3,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,99</t>
+          <t>-4,55; 1,85</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,55%</t>
+          <t>-19,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,59%</t>
+          <t>-7,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 23,63</t>
+          <t>-37,8; 24,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 4,8</t>
+          <t>-45,12; 5,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 38,2</t>
+          <t>-18,92; 39,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,87; -8,51</t>
+          <t>-47,59; -9,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,54; -22,53</t>
+          <t>-55,56; -22,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -4,99</t>
+          <t>-34,9; 0,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,18; -5,01</t>
+          <t>-36,47; -4,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -19,14</t>
+          <t>-46,02; -18,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 5,75</t>
+          <t>-20,74; 10,07</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,14</t>
+          <t>-6,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,94</t>
+          <t>-4,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,41</t>
+          <t>-4,15; -0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -2,22</t>
+          <t>-5,77; -2,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,62</t>
+          <t>-4,5; -0,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; -2,06</t>
+          <t>-6,58; -2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -5,13</t>
+          <t>-9,42; -5,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -5,63</t>
+          <t>-8,06; -4,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -1,63</t>
+          <t>-4,61; -1,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -4,16</t>
+          <t>-7,04; -4,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; -4,07</t>
+          <t>-5,68; -2,97</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,23%</t>
+          <t>-13,35%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,44%</t>
+          <t>-20,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-24,1%</t>
+          <t>-17,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -2,14</t>
+          <t>-20,3; -0,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,76; -12,03</t>
+          <t>-28,28; -11,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,38; -8,83</t>
+          <t>-21,83; -3,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,79; -6,95</t>
+          <t>-21,16; -6,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,74; -17,8</t>
+          <t>-30,86; -18,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -19,65</t>
+          <t>-26,23; -14,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,53; -6,82</t>
+          <t>-18,23; -6,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -17,41</t>
+          <t>-27,51; -17,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -17,13</t>
+          <t>-22,25; -12,39</t>
         </is>
       </c>
     </row>
